--- a/Amazon关键词监控_多数据源字段对应表_by_kong.xlsx
+++ b/Amazon关键词监控_多数据源字段对应表_by_kong.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求字段匹配表" sheetId="1" r:id="Rb0d50a29753740b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="西柚洞察" sheetId="2" r:id="R069663ede83b437c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sorftime MCP vs CLI" sheetId="3" r:id="R62236598d0a74ca3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卖家精灵" sheetId="4" r:id="Rf62a7927c011416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIF" sheetId="5" r:id="Rb5153a1965f44935"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求字段匹配表" sheetId="1" r:id="R4c60b930d47742b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="西柚洞察" sheetId="2" r:id="R251fe35754d24b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sorftime MCP vs CLI" sheetId="3" r:id="Rd08a7911307c4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卖家精灵" sheetId="4" r:id="R8d202ab3492b4b12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIF" sheetId="5" r:id="R7a2f211bf1fc45d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -76,7 +76,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -133,127 +133,52 @@
         <x:fgColor rgb="FF276B65"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7A4A14"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="34">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="138">
+  <x:cellXfs count="142">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -599,6 +524,16 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -607,7 +542,7 @@
   <x:dxfs count="1">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7FAFC"/>
         </x:patternFill>
       </x:fill>
@@ -824,8 +759,8 @@
       <x:c r="E4" s="39" t="str">
         <x:v>Sorftime CLI</x:v>
       </x:c>
-      <x:c r="F4" s="39" t="str">
-        <x:v>卖家精灵 API</x:v>
+      <x:c r="F4" s="141" t="str">
+        <x:v>卖家精灵 MCP</x:v>
       </x:c>
       <x:c r="G4" s="39" t="str">
         <x:v>SIF MCP</x:v>
@@ -930,7 +865,7 @@
         <x:v>用户输入 + 接口匹配</x:v>
       </x:c>
       <x:c r="F7" s="30" t="str">
-        <x:v>用户输入 + 接口匹配</x:v>
+        <x:v>用户输入 + MCP接口匹配</x:v>
       </x:c>
       <x:c r="G7" s="30" t="str">
         <x:v>用户输入 + 动态匹配</x:v>
@@ -965,7 +900,7 @@
         <x:v>ASINRequestKeywordv2</x:v>
       </x:c>
       <x:c r="F8" s="30" t="str">
-        <x:v>traffic_keyword · trafficPercentage</x:v>
+        <x:v>traffic_keyword → traffic_keyword_stat</x:v>
       </x:c>
       <x:c r="G8" s="30" t="str">
         <x:v>动态匹配流量/反查工具</x:v>
@@ -1000,7 +935,7 @@
         <x:v>KeywordRequest</x:v>
       </x:c>
       <x:c r="F9" s="30" t="str">
-        <x:v>keyword_research / ABA · searchRank</x:v>
+        <x:v>aba_research_monthly → aba_research_weekly</x:v>
       </x:c>
       <x:c r="G9" s="30" t="str">
         <x:v>动态匹配关键词详情/ABA工具</x:v>
@@ -1035,7 +970,7 @@
         <x:v>KeywordRequest</x:v>
       </x:c>
       <x:c r="F10" s="30" t="str">
-        <x:v>keyword_research / ABA · searches</x:v>
+        <x:v>keyword_research → aba_research_monthly/weekly</x:v>
       </x:c>
       <x:c r="G10" s="30" t="str">
         <x:v>动态匹配关键词详情工具</x:v>
@@ -1140,7 +1075,7 @@
         <x:v>ProductRequest</x:v>
       </x:c>
       <x:c r="F13" s="30" t="str">
-        <x:v>asin_detail · price</x:v>
+        <x:v>asin_detail_with_coupon_trend → asin_detail → keepa_info</x:v>
       </x:c>
       <x:c r="G13" s="30" t="str">
         <x:v>动态匹配产品详情工具</x:v>
@@ -1175,7 +1110,7 @@
         <x:v>ProductRequest（实际返回时）</x:v>
       </x:c>
       <x:c r="F14" s="30" t="str">
-        <x:v>产品详情实际返回</x:v>
+        <x:v>asin_detail_with_coupon_trend / asin_coupon_trend</x:v>
       </x:c>
       <x:c r="G14" s="30" t="str">
         <x:v>动态匹配产品详情工具</x:v>
@@ -1210,7 +1145,7 @@
         <x:v>ProductRequest（实际返回时）</x:v>
       </x:c>
       <x:c r="F15" s="30" t="str">
-        <x:v>产品详情实际返回</x:v>
+        <x:v>asin_detail_with_coupon_trend（实际返回时）</x:v>
       </x:c>
       <x:c r="G15" s="30" t="str">
         <x:v>动态匹配产品详情工具</x:v>
@@ -1245,7 +1180,7 @@
         <x:v>ProductRequest（实际返回时）</x:v>
       </x:c>
       <x:c r="F16" s="30" t="str">
-        <x:v>产品详情实际返回</x:v>
+        <x:v>asin_detail_with_coupon_trend（实际返回时）</x:v>
       </x:c>
       <x:c r="G16" s="30" t="str">
         <x:v>动态匹配产品详情工具</x:v>
@@ -1280,7 +1215,7 @@
         <x:v>ProductRequest</x:v>
       </x:c>
       <x:c r="F17" s="30" t="str">
-        <x:v>competitor_lookup / asin_sales_trend</x:v>
+        <x:v>competitor_lookup → asin_sales_trend</x:v>
       </x:c>
       <x:c r="G17" s="30" t="str">
         <x:v>动态匹配销量工具</x:v>
@@ -1315,7 +1250,7 @@
         <x:v>ProductRequest</x:v>
       </x:c>
       <x:c r="F18" s="30" t="str">
-        <x:v>asin_detail / keepa_info · 根类目BSR</x:v>
+        <x:v>asin_detail → keepa_info · 根类目BSR</x:v>
       </x:c>
       <x:c r="G18" s="30" t="str">
         <x:v>动态匹配根类目排名</x:v>
@@ -1350,7 +1285,7 @@
         <x:v>ProductRequest · 子类排名</x:v>
       </x:c>
       <x:c r="F19" s="68" t="str">
-        <x:v>asin_detail / keepa_info · 小类BSR</x:v>
+        <x:v>asin_detail → keepa_info · 小类BSR</x:v>
       </x:c>
       <x:c r="G19" s="68" t="str">
         <x:v>动态匹配子类/细分类排名</x:v>
@@ -1385,7 +1320,7 @@
         <x:v>ProductRequest</x:v>
       </x:c>
       <x:c r="F20" s="30" t="str">
-        <x:v>asin_detail · rating</x:v>
+        <x:v>asin_detail → keepa_info · rating</x:v>
       </x:c>
       <x:c r="G20" s="30" t="str">
         <x:v>动态匹配产品详情工具</x:v>
@@ -1420,7 +1355,7 @@
         <x:v>ProductRequest</x:v>
       </x:c>
       <x:c r="F21" s="30" t="str">
-        <x:v>asin_detail · ratings</x:v>
+        <x:v>asin_detail → keepa_info · ratings</x:v>
       </x:c>
       <x:c r="G21" s="30" t="str">
         <x:v>动态匹配产品详情工具</x:v>
@@ -1455,7 +1390,7 @@
         <x:v>本地按站点生成</x:v>
       </x:c>
       <x:c r="F22" s="46" t="str">
-        <x:v>本地按站点生成</x:v>
+        <x:v>接口返回或本地生成</x:v>
       </x:c>
       <x:c r="G22" s="46" t="str">
         <x:v>本地按站点生成</x:v>
